--- a/research/traditional_assets/database/data/jamaica/jamaica_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_insurance_general.xlsx
@@ -588,112 +588,106 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.09232804232804233</v>
+        <v>0.1405844155844156</v>
       </c>
       <c r="H2">
-        <v>0.09232804232804233</v>
+        <v>0.1405844155844156</v>
       </c>
       <c r="I2">
-        <v>0.2558201058201058</v>
+        <v>0.1681818181818182</v>
       </c>
       <c r="J2">
-        <v>0.2479612254506323</v>
+        <v>0.167872091076511</v>
       </c>
       <c r="K2">
-        <v>0.915</v>
+        <v>0.542</v>
       </c>
       <c r="L2">
-        <v>0.2420634920634921</v>
+        <v>0.175974025974026</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.00588235294117647</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.04059040590405903</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.00588235294117647</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.04059040590405903</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>4.86</v>
+        <v>5.08</v>
       </c>
       <c r="V2">
-        <v>1.182481751824817</v>
+        <v>1.358288770053476</v>
       </c>
       <c r="W2">
-        <v>0.4621212121212122</v>
+        <v>0.1928825622775801</v>
       </c>
       <c r="X2">
-        <v>0.08946968241099372</v>
+        <v>0.1382369265384644</v>
       </c>
       <c r="Y2">
-        <v>0.3726515297102184</v>
-      </c>
-      <c r="Z2">
-        <v>6.67844522968198</v>
-      </c>
-      <c r="AA2">
-        <v>1.655995463256873</v>
+        <v>0.05464563573911571</v>
       </c>
       <c r="AB2">
-        <v>0.08564432406016376</v>
-      </c>
-      <c r="AC2">
-        <v>1.570351139196709</v>
+        <v>0.1352768892237745</v>
       </c>
       <c r="AD2">
-        <v>0.532</v>
+        <v>0.272</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.532</v>
+        <v>0.272</v>
       </c>
       <c r="AG2">
-        <v>-4.328</v>
+        <v>-4.808</v>
       </c>
       <c r="AH2">
-        <v>0.1146057733735459</v>
+        <v>0.06779661016949153</v>
       </c>
       <c r="AI2">
-        <v>0.1591861160981448</v>
+        <v>0.07766990291262137</v>
       </c>
       <c r="AJ2">
-        <v>19.85321100917432</v>
+        <v>4.501872659176032</v>
       </c>
       <c r="AK2">
-        <v>2.851119894598155</v>
+        <v>3.046894803548796</v>
       </c>
       <c r="AL2">
-        <v>0.039</v>
+        <v>0.029</v>
       </c>
       <c r="AM2">
-        <v>0.013</v>
+        <v>0.007000000000000003</v>
       </c>
       <c r="AN2">
-        <v>0.5066666666666667</v>
+        <v>0.4641638225255973</v>
       </c>
       <c r="AO2">
-        <v>24.7948717948718</v>
+        <v>17.86206896551724</v>
       </c>
       <c r="AP2">
-        <v>-4.121904761904762</v>
+        <v>-8.204778156996587</v>
       </c>
       <c r="AQ2">
-        <v>74.38461538461537</v>
+        <v>73.99999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -713,112 +707,106 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.09232804232804233</v>
+        <v>0.1405844155844156</v>
       </c>
       <c r="H3">
-        <v>0.09232804232804233</v>
+        <v>0.1405844155844156</v>
       </c>
       <c r="I3">
-        <v>0.2558201058201058</v>
+        <v>0.1681818181818182</v>
       </c>
       <c r="J3">
-        <v>0.2479612254506323</v>
+        <v>0.167872091076511</v>
       </c>
       <c r="K3">
-        <v>0.915</v>
+        <v>0.542</v>
       </c>
       <c r="L3">
-        <v>0.2420634920634921</v>
+        <v>0.175974025974026</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.022</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.00588235294117647</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.04059040590405903</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.022</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.00588235294117647</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.04059040590405903</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>4.86</v>
+        <v>5.08</v>
       </c>
       <c r="V3">
-        <v>1.182481751824817</v>
+        <v>1.358288770053476</v>
       </c>
       <c r="W3">
-        <v>0.4621212121212122</v>
+        <v>0.1928825622775801</v>
       </c>
       <c r="X3">
-        <v>0.08946968241099372</v>
+        <v>0.1382369265384644</v>
       </c>
       <c r="Y3">
-        <v>0.3726515297102184</v>
-      </c>
-      <c r="Z3">
-        <v>6.67844522968198</v>
-      </c>
-      <c r="AA3">
-        <v>1.655995463256873</v>
+        <v>0.05464563573911571</v>
       </c>
       <c r="AB3">
-        <v>0.08564432406016376</v>
-      </c>
-      <c r="AC3">
-        <v>1.570351139196709</v>
+        <v>0.1352768892237745</v>
       </c>
       <c r="AD3">
-        <v>0.532</v>
+        <v>0.272</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.532</v>
+        <v>0.272</v>
       </c>
       <c r="AG3">
-        <v>-4.328</v>
+        <v>-4.808</v>
       </c>
       <c r="AH3">
-        <v>0.1146057733735459</v>
+        <v>0.06779661016949153</v>
       </c>
       <c r="AI3">
-        <v>0.1591861160981448</v>
+        <v>0.07766990291262137</v>
       </c>
       <c r="AJ3">
-        <v>19.85321100917432</v>
+        <v>4.501872659176032</v>
       </c>
       <c r="AK3">
-        <v>2.851119894598155</v>
+        <v>3.046894803548796</v>
       </c>
       <c r="AL3">
-        <v>0.039</v>
+        <v>0.029</v>
       </c>
       <c r="AM3">
-        <v>0.013</v>
+        <v>0.007000000000000003</v>
       </c>
       <c r="AN3">
-        <v>0.5066666666666667</v>
+        <v>0.4641638225255973</v>
       </c>
       <c r="AO3">
-        <v>24.7948717948718</v>
+        <v>17.86206896551724</v>
       </c>
       <c r="AP3">
-        <v>-4.121904761904762</v>
+        <v>-8.204778156996587</v>
       </c>
       <c r="AQ3">
-        <v>74.38461538461537</v>
+        <v>73.99999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_insurance_general.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1405844155844156</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
-        <v>0.1405844155844156</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
-        <v>0.1681818181818182</v>
+        <v>0.06760563380281691</v>
       </c>
       <c r="J2">
-        <v>0.167872091076511</v>
+        <v>0.06484622017821214</v>
       </c>
       <c r="K2">
-        <v>0.542</v>
+        <v>0.188</v>
       </c>
       <c r="L2">
-        <v>0.175974025974026</v>
+        <v>0.06619718309859156</v>
       </c>
       <c r="M2">
-        <v>0.022</v>
+        <v>0.045</v>
       </c>
       <c r="N2">
-        <v>0.00588235294117647</v>
+        <v>0.01206434316353887</v>
       </c>
       <c r="O2">
-        <v>0.04059040590405903</v>
+        <v>0.2393617021276596</v>
       </c>
       <c r="P2">
-        <v>0.022</v>
+        <v>0.045</v>
       </c>
       <c r="Q2">
-        <v>0.00588235294117647</v>
+        <v>0.01206434316353887</v>
       </c>
       <c r="R2">
-        <v>0.04059040590405903</v>
+        <v>0.2393617021276596</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,64 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.08</v>
+        <v>5.77</v>
       </c>
       <c r="V2">
-        <v>1.358288770053476</v>
+        <v>1.546916890080429</v>
       </c>
       <c r="W2">
-        <v>0.1928825622775801</v>
+        <v>0.05820433436532508</v>
       </c>
       <c r="X2">
-        <v>0.1382369265384644</v>
+        <v>0.111199752942059</v>
       </c>
       <c r="Y2">
-        <v>0.05464563573911571</v>
+        <v>-0.05299541857673395</v>
       </c>
       <c r="AB2">
-        <v>0.1352768892237745</v>
+        <v>0.109463711150903</v>
       </c>
       <c r="AD2">
-        <v>0.272</v>
+        <v>0.199</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.272</v>
+        <v>0.199</v>
       </c>
       <c r="AG2">
-        <v>-4.808</v>
+        <v>-5.571</v>
       </c>
       <c r="AH2">
-        <v>0.06779661016949153</v>
+        <v>0.05064902010689743</v>
       </c>
       <c r="AI2">
-        <v>0.07766990291262137</v>
+        <v>0.05703640011464604</v>
       </c>
       <c r="AJ2">
-        <v>4.501872659176032</v>
+        <v>3.026072786529061</v>
       </c>
       <c r="AK2">
-        <v>3.046894803548796</v>
+        <v>2.442349846558527</v>
       </c>
       <c r="AL2">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="AM2">
-        <v>0.007000000000000003</v>
+        <v>-0.0009999999999999974</v>
       </c>
       <c r="AN2">
-        <v>0.4641638225255973</v>
+        <v>0.6482084690553747</v>
       </c>
       <c r="AO2">
-        <v>17.86206896551724</v>
+        <v>9.142857142857142</v>
       </c>
       <c r="AP2">
-        <v>-8.204778156996587</v>
+        <v>-18.14657980456026</v>
       </c>
       <c r="AQ2">
-        <v>73.99999999999997</v>
+        <v>-192.0000000000005</v>
       </c>
     </row>
     <row r="3">
@@ -707,40 +707,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1405844155844156</v>
+        <v>0.2</v>
       </c>
       <c r="H3">
-        <v>0.1405844155844156</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
-        <v>0.1681818181818182</v>
+        <v>0.06760563380281691</v>
       </c>
       <c r="J3">
-        <v>0.167872091076511</v>
+        <v>0.06484622017821214</v>
       </c>
       <c r="K3">
-        <v>0.542</v>
+        <v>0.188</v>
       </c>
       <c r="L3">
-        <v>0.175974025974026</v>
+        <v>0.06619718309859156</v>
       </c>
       <c r="M3">
-        <v>0.022</v>
+        <v>0.045</v>
       </c>
       <c r="N3">
-        <v>0.00588235294117647</v>
+        <v>0.01206434316353887</v>
       </c>
       <c r="O3">
-        <v>0.04059040590405903</v>
+        <v>0.2393617021276596</v>
       </c>
       <c r="P3">
-        <v>0.022</v>
+        <v>0.045</v>
       </c>
       <c r="Q3">
-        <v>0.00588235294117647</v>
+        <v>0.01206434316353887</v>
       </c>
       <c r="R3">
-        <v>0.04059040590405903</v>
+        <v>0.2393617021276596</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -749,64 +749,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.08</v>
+        <v>5.77</v>
       </c>
       <c r="V3">
-        <v>1.358288770053476</v>
+        <v>1.546916890080429</v>
       </c>
       <c r="W3">
-        <v>0.1928825622775801</v>
+        <v>0.05820433436532508</v>
       </c>
       <c r="X3">
-        <v>0.1382369265384644</v>
+        <v>0.111199752942059</v>
       </c>
       <c r="Y3">
-        <v>0.05464563573911571</v>
+        <v>-0.05299541857673395</v>
       </c>
       <c r="AB3">
-        <v>0.1352768892237745</v>
+        <v>0.109463711150903</v>
       </c>
       <c r="AD3">
-        <v>0.272</v>
+        <v>0.199</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.272</v>
+        <v>0.199</v>
       </c>
       <c r="AG3">
-        <v>-4.808</v>
+        <v>-5.571</v>
       </c>
       <c r="AH3">
-        <v>0.06779661016949153</v>
+        <v>0.05064902010689743</v>
       </c>
       <c r="AI3">
-        <v>0.07766990291262137</v>
+        <v>0.05703640011464604</v>
       </c>
       <c r="AJ3">
-        <v>4.501872659176032</v>
+        <v>3.026072786529061</v>
       </c>
       <c r="AK3">
-        <v>3.046894803548796</v>
+        <v>2.442349846558527</v>
       </c>
       <c r="AL3">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="AM3">
-        <v>0.007000000000000003</v>
+        <v>-0.0009999999999999974</v>
       </c>
       <c r="AN3">
-        <v>0.4641638225255973</v>
+        <v>0.6482084690553747</v>
       </c>
       <c r="AO3">
-        <v>17.86206896551724</v>
+        <v>9.142857142857142</v>
       </c>
       <c r="AP3">
-        <v>-8.204778156996587</v>
+        <v>-18.14657980456026</v>
       </c>
       <c r="AQ3">
-        <v>73.99999999999997</v>
+        <v>-192.0000000000005</v>
       </c>
     </row>
   </sheetData>
